--- a/Java基礎⑥_クラスの基礎_演習問題.xlsx
+++ b/Java基礎⑥_クラスの基礎_演習問題.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\村石 莉彩\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41414D1-6F90-460B-BA0C-F1CB1706AEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BA5C08-EFE4-4534-8D68-CCB9845C69EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-6510" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-6690" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="はじめに" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="82">
   <si>
     <t>【前提事項】</t>
   </si>
@@ -142,171 +142,181 @@
     <t>mainメソッドで2つの整数を足し算し、結果を表示してください。</t>
   </si>
   <si>
+    <t>命名規則</t>
+  </si>
+  <si>
+    <t>次の変数名・メソッド名・クラス名を、正しい命名規則（camelCase / PascalCase / UPPER_SNAKE_CASE）に直してください。</t>
+  </si>
+  <si>
+    <t>① student_name（変数名）　② Calc_score（メソッド名）　③ my class（クラス名）　④ max_count（定数名）</t>
+  </si>
+  <si>
+    <t>以下の名前はどの命名規則に当たるか答えてください。</t>
+  </si>
+  <si>
+    <t>① getUserName　② MAX_RETRY_COUNT　③ StudentRecord　④ total_price</t>
+  </si>
+  <si>
+    <t>次の説明に合う名前を、適切な命名規則を使って自分で考えてください。</t>
+  </si>
+  <si>
+    <t>① 「ユーザーのメールアドレス」を表す変数名</t>
+  </si>
+  <si>
+    <t>② 「メールを送信する」処理を表すメソッド名</t>
+  </si>
+  <si>
+    <t>引数と戻り値</t>
+  </si>
+  <si>
+    <t>引数として名前（String型）を受け取り、「こんにちは、〇〇さん！」と表示するメソッド greet() を作成してください。</t>
+  </si>
+  <si>
+    <t>mainメソッドから greet() を呼び出して動作を確認してください。</t>
+  </si>
+  <si>
+    <t>mainメソッドで add() を呼び出し、結果を変数に受け取って表示してください。</t>
+  </si>
+  <si>
+    <t>mainメソッドからいくつかの数値で呼び出して結果を確認してください。</t>
+  </si>
+  <si>
+    <t>以下の incomplete なメソッドを完成させてください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // wordをtimes回繰り返した文字列を返す</t>
+  </si>
+  <si>
+    <t>mainメソッドから repeat("Java", 3) のように呼び出し、「JavaJavaJava」と表示されることを確認してください。</t>
+  </si>
+  <si>
+    <t>半径（double型）を引数として受け取り、円の面積（π × r²）を計算して返すメソッド calcArea() を作成してください。</t>
+  </si>
+  <si>
+    <t>Math.PI を使って計算し、mainメソッドから呼び出して結果を表示してください。</t>
+  </si>
+  <si>
+    <t>studentName</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>calcScore</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MyClass</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MAX_COUNT</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャメルケース</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アッパースネークケース</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パスカルケース</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スネークケース</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>userMail</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sendMail</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>③ 「銀行口座」を表すクラス名</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BankAccount</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>④ 「消費税率（変更不可）」を表す定数名</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CONSUMPTION_TAX_RATE</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス「Person」を作成し、名前（name）と年齢（age）のフィールドを持たせてください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス「Book」を作成し、タイトル（title）、著者（author）、価格（price）をフィールドに持たせてください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス「Student」を作成し、名前と成績（配列）を持たせてください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成績の平均を計算して表示するメソッドを作成してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス「Employee」を作成し、ID、名前、給与をフィールドとして持たせてください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>給与を昇給させるraiseSalary(double percent)メソッドを実装し、昇給後の給与を表示してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス「Circle」を作成し、半径（radius）をフィールドとして持たせてください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンストラクタで半径を初期化し、面積（π × r²）を計算して表示するメソッドを実装してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス「Dog」を作成し、名前（name）フィールドを持たせてください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>インスタンスを生成して名前を設定し、名前を表示してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>mainメソッドでコマンドライン引数を受け取り、その値をコンソールに表示してください。</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>mainメソッド内で、複数のクラスをインスタンス化し、それぞれのメソッドを呼び出してください。</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>mainメソッド内で、自分の名前と年齢を変数に代入し、自己紹介文を表示してください。</t>
-  </si>
-  <si>
-    <t>命名規則</t>
-  </si>
-  <si>
-    <t>次の変数名・メソッド名・クラス名を、正しい命名規則（camelCase / PascalCase / UPPER_SNAKE_CASE）に直してください。</t>
-  </si>
-  <si>
-    <t>① student_name（変数名）　② Calc_score（メソッド名）　③ my class（クラス名）　④ max_count（定数名）</t>
-  </si>
-  <si>
-    <t>以下の名前はどの命名規則に当たるか答えてください。</t>
-  </si>
-  <si>
-    <t>① getUserName　② MAX_RETRY_COUNT　③ StudentRecord　④ total_price</t>
-  </si>
-  <si>
-    <t>次の説明に合う名前を、適切な命名規則を使って自分で考えてください。</t>
-  </si>
-  <si>
-    <t>① 「ユーザーのメールアドレス」を表す変数名</t>
-  </si>
-  <si>
-    <t>② 「メールを送信する」処理を表すメソッド名</t>
-  </si>
-  <si>
-    <t>引数と戻り値</t>
-  </si>
-  <si>
-    <t>引数として名前（String型）を受け取り、「こんにちは、〇〇さん！」と表示するメソッド greet() を作成してください。</t>
-  </si>
-  <si>
-    <t>mainメソッドから greet() を呼び出して動作を確認してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>問1.</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>2つの整数を引数として受け取り、その合計を戻り値として返すメソッド add() を作成してください。</t>
-  </si>
-  <si>
-    <t>mainメソッドで add() を呼び出し、結果を変数に受け取って表示してください。</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>整数を引数として受け取り、その数が偶数なら true、奇数なら false を返すメソッド isEven() を作成してください。</t>
-  </si>
-  <si>
-    <t>mainメソッドからいくつかの数値で呼び出して結果を確認してください。</t>
-  </si>
-  <si>
-    <t>以下の incomplete なメソッドを完成させてください。</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>public static String repeat(String word, int times) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    // wordをtimes回繰り返した文字列を返す</t>
-  </si>
-  <si>
-    <t>mainメソッドから repeat("Java", 3) のように呼び出し、「JavaJavaJava」と表示されることを確認してください。</t>
-  </si>
-  <si>
-    <t>半径（double型）を引数として受け取り、円の面積（π × r²）を計算して返すメソッド calcArea() を作成してください。</t>
-  </si>
-  <si>
-    <t>Math.PI を使って計算し、mainメソッドから呼び出して結果を表示してください。</t>
-  </si>
-  <si>
-    <t>studentName</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>calcScore</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MyClass</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MAX_COUNT</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>キャメルケース</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アッパースネークケース</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>パスカルケース</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スネークケース</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>userMail</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>sendMail</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>③ 「銀行口座」を表すクラス名</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>BankAccount</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>④ 「消費税率（変更不可）」を表す定数名</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CONSUMPTION_TAX_RATE</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クラス「Person」を作成し、名前（name）と年齢（age）のフィールドを持たせてください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クラス「Book」を作成し、タイトル（title）、著者（author）、価格（price）をフィールドに持たせてください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クラス「Student」を作成し、名前と成績（配列）を持たせてください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>成績の平均を計算して表示するメソッドを作成してください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クラス「Employee」を作成し、ID、名前、給与をフィールドとして持たせてください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>給与を昇給させるraiseSalary(double percent)メソッドを実装し、昇給後の給与を表示してください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クラス「Circle」を作成し、半径（radius）をフィールドとして持たせてください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>コンストラクタで半径を初期化し、面積（π × r²）を計算して表示するメソッドを実装してください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クラス「Dog」を作成し、名前（name）フィールドを持たせてください。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>インスタンスを生成して名前を設定し、名前を表示してください。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -314,7 +324,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -742,17 +752,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="80" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="22.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" ht="36" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -766,91 +776,91 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="18.600000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="B13" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="B17" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -862,37 +872,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="18.600000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -900,52 +910,52 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2">
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2">
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2">
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2">
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2">
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2">
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2">
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2">
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2">
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -953,7 +963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -961,12 +971,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2">
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
@@ -974,12 +984,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2">
       <c r="B29" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -987,7 +997,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:2">
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
@@ -1001,24 +1011,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.8984375" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="18.600000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1026,7 +1036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1034,28 +1044,28 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1067,28 +1077,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="4" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1101,10 +1111,10 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1117,29 +1127,29 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1153,12 +1163,12 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1171,10 +1181,10 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1187,29 +1197,29 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1223,12 +1233,12 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1241,17 +1251,17 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1259,17 +1269,17 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1277,17 +1287,17 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1295,17 +1305,17 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1313,7 +1323,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1327,7 +1337,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1341,7 +1351,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1355,7 +1365,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1378,28 +1388,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="4" customWidth="1"/>
     <col min="2" max="2" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1413,10 +1423,10 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1430,7 +1440,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1445,7 +1455,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1460,12 +1470,12 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1479,10 +1489,10 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1496,7 +1506,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1511,7 +1521,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1526,12 +1536,12 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1545,10 +1555,10 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1562,7 +1572,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1577,7 +1587,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1592,12 +1602,12 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -1611,10 +1621,10 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1628,10 +1638,10 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1645,7 +1655,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>21</v>
@@ -1662,10 +1672,10 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1679,7 +1689,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1694,7 +1704,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1709,12 +1719,12 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1728,10 +1738,10 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1745,7 +1755,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1760,7 +1770,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1989,15 +1999,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
@@ -2006,6 +2007,15 @@
     <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2028,14 +2038,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FE82F00-139C-445B-BABD-B2DB457293CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26117E70-7922-4B8A-B7BC-95B90620D5B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2044,4 +2046,12 @@
     <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FE82F00-139C-445B-BABD-B2DB457293CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>